--- a/docs/downloads/09/t8_transition_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/09/t8_transition_alaotra_ambatoharanana.xlsx
@@ -489,12 +489,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
